--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -1,27 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mzees\PycharmProjects\POSAutomation\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751E8CE3-04DA-4F86-B02E-20B172471C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Tags" sheetId="1" r:id="rId1"/>
-    <sheet name="TestConfigs" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="RunConfig" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Tags" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="TestConfigs" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>emulator</t>
+  </si>
+  <si>
+    <t>emulator or real_device - matches config/config.yaml</t>
+  </si>
+  <si>
+    <t>Suite</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>Smoke</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
   <si>
     <t>FilePath</t>
   </si>
@@ -35,61 +60,52 @@
     <t>Date Added</t>
   </si>
   <si>
-    <t>tests/login/test_login.py</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>tests/shift/test_clock_in.py</t>
-  </si>
-  <si>
     <t>tests/sale_order/test_create_sale_order.py</t>
   </si>
   <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>tests/sale_order/test_split_payment.py</t>
+  </si>
+  <si>
+    <t>tests/sale_return/test_sale_return.py</t>
+  </si>
+  <si>
+    <t>tests/sales_history/test_void_payment.py</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>tests/sales_history/test_edit_order.py</t>
+  </si>
+  <si>
     <t>ConfigName</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>clock_in_pin</t>
   </si>
   <si>
-    <t>1234</t>
-  </si>
-  <si>
     <t>PIN used for Clock In on the emulator's Demo Admin account</t>
   </si>
   <si>
     <t>discount_percent</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>Default Additional Discount percentage applied in sale order tests</t>
   </si>
   <si>
     <t>tobacco_product_1_upc</t>
   </si>
   <si>
-    <t>4210691878</t>
-  </si>
-  <si>
     <t>First MSA/tobacco product UPC (triggers age verification)</t>
   </si>
   <si>
     <t>tobacco_product_2_upc</t>
-  </si>
-  <si>
-    <t>2194227147</t>
   </si>
   <si>
     <t>Second MSA/tobacco product UPC (age verification must not reappear)</t>
@@ -107,14 +123,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -144,7 +160,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -231,6 +247,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,6 +282,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -299,20 +317,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -434,151 +448,273 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.714285714285715" customWidth="1"/>
+    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="21.142857142857142" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="42.142857142857146" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>1234</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>4210691878</v>
+      </c>
       <c r="C4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>2194227147</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>